--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/region-de-los-lagos.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/region-de-los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1393093-673-CM26</t>
+          <t>5413-5-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>METASOFT SOCIEDAD POR ACCIONES</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.213.064-5</t>
+          <t>77.077.350-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,6 +569,677 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
+        <v>31499.71</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2328-26-CM25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ene-2025</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>VICTORIA SpA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>76.188.587-1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>8852.549999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1057539-8836-CM25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>77.592.300-8</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>29569.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1057539-16153-CM25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>76.132.093-9</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>58749.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1057539-16834-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>76.132.093-9</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>36693.08</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5413-533-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>70.772.100-6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>77.077.350-4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>69696.74000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1057539-20176-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.132.093-9</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>63154.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1057539-20177-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76.132.093-9</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>56727.35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1057539-20625-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SISTEMAS EXPERTOS E INGENIERIA DE SOFTWARE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>76.132.093-9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>62924.68</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>752-364-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>72.221.800-0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Zecovery Ltda   -    EXEC</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>62422.76</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2307-3666-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.210.100-6</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>77.592.300-8</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>34816.93</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1393093-673-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.981.360-K</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>METASOFT SOCIEDAD POR ACCIONES</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>76.213.064-5</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
         <v>42005.51</v>
       </c>
     </row>
